--- a/Data/Testdata/EndToEnd.xlsx
+++ b/Data/Testdata/EndToEnd.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github.com\rpapub\PurposefulPromethium\Data\Testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E4A7272-E43F-4648-A8B9-30B7140951B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{606696EE-C0B1-43FB-9A90-2D0ED8DF7872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="4065" windowWidth="21600" windowHeight="11835" xr2:uid="{F74654AC-9CBE-4B04-82D5-CDC073D5687E}"/>
+    <workbookView xWindow="1095" yWindow="3540" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{F74654AC-9CBE-4B04-82D5-CDC073D5687E}"/>
   </bookViews>
   <sheets>
     <sheet name="generic" sheetId="1" r:id="rId1"/>
+    <sheet name="MailboxAutomation" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Data\Config_Prod.xlsx</t>
   </si>
@@ -58,6 +59,15 @@
   </si>
   <si>
     <t>in_Environment</t>
+  </si>
+  <si>
+    <t>in_CountMailsIncomingExpected</t>
+  </si>
+  <si>
+    <t>in_CountMailsHandoverExpected</t>
+  </si>
+  <si>
+    <t>in_CountMailsSuccExpected</t>
   </si>
 </sst>
 </file>
@@ -431,6 +441,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F330C4B-B3EA-46BC-B3F3-CF06A86546EA}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -462,6 +476,54 @@
       </c>
       <c r="B4" t="s">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11FCFAD0-3FC3-46A2-8BDD-DD23115279D8}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
